--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:12</t>
+    <t xml:space="preserve">2026-09-09 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:06</t>
+    <t xml:space="preserve">2026-09-17 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:03</t>
+    <t xml:space="preserve">2026-09-23 12:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:32</t>
+    <t xml:space="preserve">2026-10-02 14:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:15</t>
+    <t xml:space="preserve">2026-10-05 10:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -544,7 +544,7 @@
         <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>800734.62</v>
+        <v>800734.63</v>
       </c>
     </row>
   </sheetData>
